--- a/Robot Arm Parts - Lowest.xlsx
+++ b/Robot Arm Parts - Lowest.xlsx
@@ -398,21 +398,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H17"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="55.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="70.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="80.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Lowest</v>
       </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -421,6 +432,50 @@
       <c r="B2" t="str">
         <v>2026-02-28</v>
       </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -499,7 +554,7 @@
         <v>20.4</v>
       </c>
       <c r="H6" t="str">
-        <v>Exact ST/SC serial bus board for the leader arm.</v>
+        <v>Exact repo board ASIN. LeRobot requires ST/SC serial bus support and B-channel jumpers during setup. Official board docs list 9-12.6V input, which conflicts with the repo's 5V leader PSU guidance.</v>
       </c>
     </row>
     <row r="7">
@@ -534,26 +589,26 @@
         <v>Leader</v>
       </c>
       <c r="B8" t="str">
-        <v>5V 5A Power Adapter 25W AC 100-240V to DC Wall Power Supply Converter with 5.5x2.5mm/2.1mm Plug</v>
+        <v>Facmogu DC 5V 4A AC to DC Converter, AC 100-240V to DC 5 Volt 4 Amp 20W Power Supply 5V Switching Transformer Power Adapter, Wall Mounted Adapter with with Barrel Connector 5.5x2.5mm &amp; 5.5x2.1mm</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.amazon.ca/MTDZKJG-100-240V-Converter-5-5x2-5mm-Security/dp/B0CJHQNFMG</v>
+        <v>https://www.amazon.ca/Facmogu-Switching-Transformer-Converter-Compatible/dp/B087LY41PV</v>
       </c>
       <c r="E8">
-        <v>26.41</v>
+        <v>14.39</v>
       </c>
       <c r="F8">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>C8*E8+F8</f>
-        <v>31.92</v>
+        <v>14.39</v>
       </c>
       <c r="H8" t="str">
-        <v>Leader-side power supply with 5.5x2.1mm compatibility.</v>
+        <v>Exact SO-101 repo PSU ASIN. Upstream controller-board voltage guidance conflicts with the repo's 5V leader supply recommendation.</v>
       </c>
     </row>
     <row r="9">
@@ -580,7 +635,7 @@
         <v>199.77</v>
       </c>
       <c r="H9" t="str">
-        <v>Buy 3 packs to get the 6x 12V follower servos required for the shared 12V rail.</v>
+        <v>Buy 3 packs to get the 6x 12V follower servos required for the shared 12V rail. Listing explicitly says 2 servos; accessory/cable contents are not explicit.</v>
       </c>
     </row>
     <row r="10">
@@ -607,7 +662,7 @@
         <v>20.4</v>
       </c>
       <c r="H10" t="str">
-        <v>Exact ST/SC serial bus board for the follower arm.</v>
+        <v>Exact repo board ASIN. Set jumpers to B-channel (USB) during LeRobot motor setup. Works with ST/SC serial bus servos.</v>
       </c>
     </row>
     <row r="11">
@@ -688,7 +743,7 @@
         <v>7.33</v>
       </c>
       <c r="H13" t="str">
-        <v>Arm hardware fill-in for M2x6 requirements.</v>
+        <v>Matches LeRobot's M2x6 requirement for the arms. Two-arm build needs about 47 M2x6 screws from the HF assembly steps.</v>
       </c>
     </row>
     <row r="14">
@@ -715,34 +770,88 @@
         <v>10.49</v>
       </c>
       <c r="H14" t="str">
-        <v>Arm hardware fill-in including M3x6 screws.</v>
+        <v>Current Amazon-only placeholder. Local LeRobot assembly docs call for M3x6 pan-head screws; this row is not an exact head-type match.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v>TOTAL: Lowest Items (CAD)</v>
       </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
       <c r="G15">
         <f>SUM(G5:G14)</f>
-        <v>523.82</v>
+        <v>506.29</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v>HST 13% (CAD)</v>
       </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
       <c r="G16">
         <f>ROUND(G15*0.13,2)</f>
-        <v>68.1</v>
+        <v>65.82</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
         <v>GRAND TOTAL (CAD)</v>
       </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
       <c r="G17">
         <f>G15+G16</f>
-        <v>591.92</v>
+        <v>572.11</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
